--- a/data/trans_bre/P15-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P15-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,72; -0,69</t>
+          <t>-6,09; -0,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,4</t>
+          <t>-3,7; 2,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,62</t>
+          <t>-1,49; 3,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,58</t>
+          <t>-3,5; 1,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,53; -7,0</t>
+          <t>-60,32; -4,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 34,34</t>
+          <t>-37,35; 38,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 74,32</t>
+          <t>-21,3; 74,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,9; 29,86</t>
+          <t>-39,44; 34,16</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,28; -0,18</t>
+          <t>-4,95; -0,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,67</t>
+          <t>-3,45; 1,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,76</t>
+          <t>-3,21; 0,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 3,97</t>
+          <t>-2,34; 3,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,08; -2,0</t>
+          <t>-49,48; -1,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 24,87</t>
+          <t>-36,93; 22,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,97; 17,51</t>
+          <t>-47,76; 17,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 105,41</t>
+          <t>-31,76; 109,77</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,74</t>
+          <t>-4,23; 0,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,45</t>
+          <t>-3,24; 2,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 1,1</t>
+          <t>-2,92; 1,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,17</t>
+          <t>-2,87; 3,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,44; 15,43</t>
+          <t>-51,74; 13,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 38,91</t>
+          <t>-34,99; 37,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-50,51; 31,09</t>
+          <t>-48,87; 32,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 96,24</t>
+          <t>-49,23; 87,95</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,63</t>
+          <t>-3,42; 0,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,13; -0,14</t>
+          <t>-5,04; 0,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,73</t>
+          <t>-2,66; 1,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,85</t>
+          <t>-2,43; 2,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 12,98</t>
+          <t>-48,83; 14,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,16; -1,54</t>
+          <t>-45,57; 0,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 32,28</t>
+          <t>-34,95; 33,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,23; 36,89</t>
+          <t>-31,63; 38,87</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -1,03</t>
+          <t>-3,42; -1,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,03</t>
+          <t>-2,26; 0,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,69</t>
+          <t>-1,67; 0,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,57</t>
+          <t>-1,37; 1,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-42,52; -14,97</t>
+          <t>-42,74; -15,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 0,51</t>
+          <t>-25,06; 2,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 13,38</t>
+          <t>-26,6; 11,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 30,97</t>
+          <t>-21,49; 31,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P15-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P15-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-9,4%</t>
+          <t>-11,03%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,09; -0,59</t>
+          <t>-5,61; -0,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 2,56</t>
+          <t>-3,93; 1,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,7</t>
+          <t>-1,6; 3,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,85</t>
+          <t>-3,6; 1,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-60,32; -4,58</t>
+          <t>-57,37; -6,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,35; 38,64</t>
+          <t>-39,48; 29,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 74,91</t>
+          <t>-23,13; 80,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,44; 34,16</t>
+          <t>-39,29; 28,08</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>-1,27</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>-17,77%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,95; -0,16</t>
+          <t>-5,26; -0,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,5</t>
+          <t>-3,3; 1,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,78</t>
+          <t>-3,24; 0,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 3,68</t>
+          <t>-3,89; 1,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,48; -1,74</t>
+          <t>-52,29; -3,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 22,46</t>
+          <t>-33,8; 25,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 17,55</t>
+          <t>-46,37; 18,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,76; 109,77</t>
+          <t>-43,7; 19,04</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>1,99</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>48,37%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,72</t>
+          <t>-4,37; 1,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,27</t>
+          <t>-3,02; 2,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,19</t>
+          <t>-2,87; 1,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 3,07</t>
+          <t>0,0; 4,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,74; 13,58</t>
+          <t>-52,4; 22,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,99; 37,9</t>
+          <t>-32,95; 36,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 32,99</t>
+          <t>-48,39; 39,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-49,23; 87,95</t>
+          <t>-2,83; 139,55</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-0,79%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 0,58</t>
+          <t>-3,42; 0,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 0,04</t>
+          <t>-5,25; -0,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,73</t>
+          <t>-2,65; 1,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 2,05</t>
+          <t>-2,05; 1,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 14,18</t>
+          <t>-48,4; 10,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,57; 0,83</t>
+          <t>-47,75; -0,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,95; 33,58</t>
+          <t>-35,71; 33,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 38,87</t>
+          <t>-26,84; 38,72</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>-0,65%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,42; -1,04</t>
+          <t>-3,4; -1,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,18</t>
+          <t>-2,56; 0,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,6</t>
+          <t>-1,53; 0,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,55</t>
+          <t>-1,14; 1,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-42,74; -15,09</t>
+          <t>-42,0; -15,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 2,46</t>
+          <t>-28,57; 1,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 11,55</t>
+          <t>-24,2; 10,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 31,86</t>
+          <t>-16,53; 19,23</t>
         </is>
       </c>
     </row>
